--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="255796" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="262242" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>
@@ -3758,16 +3758,16 @@
   <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="true"/>
-    <col min="2" max="2" width="7" customWidth="true"/>
-    <col min="3" max="3" width="11.28515625" customWidth="true"/>
-    <col min="4" max="4" width="17.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13" customWidth="true"/>
-    <col min="7" max="7" width="8.5703125" customWidth="true"/>
-    <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="175.42578125" customWidth="true"/>
-    <col min="10" max="10" width="9.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.08984375" customWidth="true"/>
+    <col min="2" max="2" width="6.54296875" customWidth="true"/>
+    <col min="3" max="3" width="10.36328125" customWidth="true"/>
+    <col min="4" max="4" width="16.36328125" customWidth="true"/>
+    <col min="5" max="5" width="11.81640625" customWidth="true"/>
+    <col min="6" max="6" width="11.90625" customWidth="true"/>
+    <col min="7" max="7" width="7.90625" customWidth="true"/>
+    <col min="8" max="8" width="36.26953125" customWidth="true"/>
+    <col min="9" max="9" width="167.54296875" customWidth="true"/>
+    <col min="10" max="10" width="9.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="262242" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="265465" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="265465" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="284803" uniqueCount="1232">
   <si>
     <t>Year</t>
   </si>
@@ -3758,16 +3758,16 @@
   <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="167.54296875" customWidth="true"/>
-    <col min="10" max="10" width="9.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="175.42578125" customWidth="true"/>
+    <col min="10" max="10" width="9.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
